--- a/tabtools/qa/output/tablex_numfmt_t3.xlsx
+++ b/tabtools/qa/output/tablex_numfmt_t3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="18">
   <si>
     <t>Table</t>
   </si>
@@ -76,10 +76,528 @@
   <numFmts count="1">
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="123">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="245">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -608,7 +1126,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="89">
+  <borders count="177">
     <border>
       <left/>
       <right/>
@@ -1208,11 +1726,603 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -1551,6 +2661,346 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="122" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0"/>
+    <xf numFmtId="166" fontId="123" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="124" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="125" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="127" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="128" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="129" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="130" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="131" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="214" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="215" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="216" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="218" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="219" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="220" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="224" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="226" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="228" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="232" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="234" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="236" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="240" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="242" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="244" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1566,110 +3016,110 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="3" customWidth="true"/>
-    <col min="3" max="5" width="15.7109375" style="4" customWidth="true"/>
+    <col min="1" max="1" width="2.7109375" style="90" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="91" customWidth="true"/>
+    <col min="3" max="5" width="15.7109375" style="92" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="34" t="s">
+    <row r="1" s="89" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="122" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="156" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="152" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="61" t="s">
+      <c r="D3" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="157" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="78">
+      <c r="C4" s="166">
         <v>6072.4230769230771</v>
       </c>
-      <c r="D4" s="79">
+      <c r="D4" s="167">
         <v>19.82692307692308</v>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="168">
         <v>3317.1153846153852</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="169" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="82">
+      <c r="C5" s="170">
         <v>6384.681818181818</v>
       </c>
-      <c r="D5" s="83">
+      <c r="D5" s="171">
         <v>24.77272727272727</v>
       </c>
-      <c r="E5" s="84">
+      <c r="E5" s="172">
         <v>2315.909090909091</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="173" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="86">
+      <c r="C6" s="174">
         <v>6165.2567567567567</v>
       </c>
-      <c r="D6" s="87">
+      <c r="D6" s="175">
         <v>21.297297297297298</v>
       </c>
-      <c r="E6" s="88">
+      <c r="E6" s="176">
         <v>3019.45945945946</v>
       </c>
     </row>
